--- a/Resources/Sheet/QuanSo.xlsx
+++ b/Resources/Sheet/QuanSo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e9c90a627767d9b/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{CD98DD43-05BF-460C-A8F7-2069D20770D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{488B2C3E-CA0D-4B42-B2A8-60D909F84D9F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC920E6-9619-4528-9CA0-37A58056C8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,9 +96,6 @@
     <t>1. Trong biên chế</t>
   </si>
   <si>
-    <t>cBB</t>
-  </si>
-  <si>
     <t>2. LL tăng cường</t>
   </si>
   <si>
@@ -214,6 +211,9 @@
   </si>
   <si>
     <t>1bVTB/e</t>
+  </si>
+  <si>
+    <t>cBB7</t>
   </si>
 </sst>
 </file>
@@ -423,7 +423,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -436,10 +436,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -710,7 +706,7 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -842,59 +838,59 @@
         <v>0</v>
       </c>
       <c r="B6" s="1">
-        <f>B7+B9</f>
+        <f t="shared" ref="B6:O6" si="0">B7+B9</f>
         <v>1001</v>
       </c>
       <c r="C6" s="1">
-        <f>C7+C9</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="D6" s="1">
-        <f>D7+D9</f>
+        <f t="shared" si="0"/>
         <v>486</v>
       </c>
       <c r="E6" s="1">
-        <f>E7+E9</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="F6" s="1">
-        <f>F7+F9</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="G6" s="1">
-        <f>G7+G9</f>
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
       <c r="H6" s="1">
-        <f>H7+H9</f>
+        <f t="shared" si="0"/>
         <v>2403</v>
       </c>
       <c r="I6" s="1">
-        <f>I7+I9</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="J6" s="1">
-        <f>J7+J9</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="K6" s="1">
-        <f>K7+K9</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="L6" s="1">
-        <f>L7+L9</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="M6" s="1">
-        <f>M7+M9</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="N6" s="1">
-        <f>N7+N9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <f>O7+O9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -907,61 +903,61 @@
         <v>546</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" ref="C7:O7" si="0">C8</f>
+        <f t="shared" ref="C7:O7" si="1">C8</f>
         <v>22</v>
       </c>
       <c r="D7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>289</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1444</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="18">
       <c r="A8" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="7">
         <v>546</v>
@@ -1008,68 +1004,68 @@
     </row>
     <row r="9" spans="1:15" ht="17.399999999999999">
       <c r="A9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="5">
-        <f t="shared" ref="B9:O9" si="1">SUM(B10:B21)</f>
+        <f t="shared" ref="B9:O9" si="2">SUM(B10:B21)</f>
         <v>455</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>197</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>959</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="N9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="18">
       <c r="A10" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="7">
         <v>74</v>
@@ -1116,7 +1112,7 @@
     </row>
     <row r="11" spans="1:15" ht="18">
       <c r="A11" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="7">
         <v>69</v>
@@ -1163,7 +1159,7 @@
     </row>
     <row r="12" spans="1:15" ht="18">
       <c r="A12" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="7">
         <v>82</v>
@@ -1210,7 +1206,7 @@
     </row>
     <row r="13" spans="1:15" ht="18">
       <c r="A13" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="7">
         <v>28</v>
@@ -1257,7 +1253,7 @@
     </row>
     <row r="14" spans="1:15" ht="18">
       <c r="A14" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="10">
         <v>3</v>
@@ -1304,7 +1300,7 @@
     </row>
     <row r="15" spans="1:15" ht="18">
       <c r="A15" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="10">
         <v>19</v>
@@ -1351,7 +1347,7 @@
     </row>
     <row r="16" spans="1:15" ht="18">
       <c r="A16" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7">
         <v>66</v>
@@ -1398,7 +1394,7 @@
     </row>
     <row r="17" spans="1:15" ht="18">
       <c r="A17" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="7">
         <v>3</v>
@@ -1443,7 +1439,7 @@
     </row>
     <row r="18" spans="1:15" ht="18">
       <c r="A18" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="7">
         <v>111</v>
@@ -1656,7 +1652,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -1788,59 +1784,59 @@
         <v>0</v>
       </c>
       <c r="B6" s="1">
-        <f>B7+B9</f>
+        <f t="shared" ref="B6:O6" si="0">B7+B9</f>
         <v>308</v>
       </c>
       <c r="C6" s="1">
-        <f>C7+C9</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="D6" s="1">
-        <f>D7+D9</f>
+        <f t="shared" si="0"/>
         <v>161</v>
       </c>
       <c r="E6" s="1">
-        <f>E7+E9</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="F6" s="1">
-        <f>F7+F9</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G6" s="1">
-        <f>G7+G9</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="H6" s="1">
-        <f>H7+H9</f>
+        <f t="shared" si="0"/>
         <v>846</v>
       </c>
       <c r="I6" s="1">
-        <f>I7+I9</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="J6" s="1">
-        <f>J7+J9</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="K6" s="1">
-        <f>K7+K9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <f>L7+L9</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="M6" s="1">
-        <f>M7+M9</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N6" s="1">
-        <f>N7+N9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <f>O7+O9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1853,61 +1849,61 @@
         <v>111</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" ref="C7:O7" si="0">C8</f>
+        <f t="shared" ref="C7:O7" si="1">C8</f>
         <v>4</v>
       </c>
       <c r="D7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>346</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="18">
       <c r="A8" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="7">
         <v>111</v>
@@ -1954,68 +1950,68 @@
     </row>
     <row r="9" spans="1:15" ht="17.399999999999999">
       <c r="A9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="5">
         <f>SUM(B10:B18)</f>
         <v>197</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" ref="C9:O9" si="1">SUM(C10:C18)</f>
+        <f t="shared" ref="C9:O9" si="2">SUM(C10:C18)</f>
         <v>8</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>500</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="18">
       <c r="A10" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="7">
         <v>29</v>
@@ -2062,7 +2058,7 @@
     </row>
     <row r="11" spans="1:15" ht="18">
       <c r="A11" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="7">
         <v>34</v>
@@ -2109,7 +2105,7 @@
     </row>
     <row r="12" spans="1:15" ht="18">
       <c r="A12" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="7">
         <v>35</v>
@@ -2156,7 +2152,7 @@
     </row>
     <row r="13" spans="1:15" ht="18">
       <c r="A13" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="7">
         <v>82</v>
@@ -2202,7 +2198,7 @@
     </row>
     <row r="14" spans="1:15" ht="18">
       <c r="A14" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="10">
         <v>1</v>
@@ -2249,7 +2245,7 @@
     </row>
     <row r="15" spans="1:15" ht="18">
       <c r="A15" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="10">
         <v>7</v>
@@ -2296,7 +2292,7 @@
     </row>
     <row r="16" spans="1:15" ht="18">
       <c r="A16" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="7">
         <v>9</v>
@@ -2462,7 +2458,7 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -2594,59 +2590,59 @@
         <v>0</v>
       </c>
       <c r="B6" s="1">
-        <f>B7+B9</f>
+        <f t="shared" ref="B6:O6" si="0">B7+B9</f>
         <v>196</v>
       </c>
       <c r="C6" s="1">
-        <f>C7+C9</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="D6" s="1">
-        <f>D7+D9</f>
+        <f t="shared" si="0"/>
         <v>96</v>
       </c>
       <c r="E6" s="1">
-        <f>E7+E9</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F6" s="1">
-        <f>F7+F9</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G6" s="1">
-        <f>G7+G9</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="H6" s="1">
-        <f>H7+H9</f>
+        <f t="shared" si="0"/>
         <v>514</v>
       </c>
       <c r="I6" s="1">
-        <f>I7+I9</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="J6" s="1">
-        <f>J7+J9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <f>K7+K9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <f>L7+L9</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="M6" s="1">
-        <f>M7+M9</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N6" s="1">
-        <f>N7+N9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <f>O7+O9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2659,61 +2655,61 @@
         <v>111</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" ref="C7:O7" si="0">C8</f>
+        <f t="shared" ref="C7:O7" si="1">C8</f>
         <v>4</v>
       </c>
       <c r="D7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>346</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="18">
       <c r="A8" s="6" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B8" s="7">
         <v>111</v>
@@ -2760,68 +2756,68 @@
     </row>
     <row r="9" spans="1:15" ht="17.399999999999999">
       <c r="A9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="5">
-        <f t="shared" ref="B9:O9" si="1">SUM(B10:B15)</f>
+        <f t="shared" ref="B9:O9" si="2">SUM(B10:B15)</f>
         <v>85</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>168</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="N9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="18">
       <c r="A10" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="7">
         <v>29</v>
@@ -2868,7 +2864,7 @@
     </row>
     <row r="11" spans="1:15" ht="18">
       <c r="A11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="7">
         <v>17</v>
@@ -2915,7 +2911,7 @@
     </row>
     <row r="12" spans="1:15" ht="18">
       <c r="A12" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="7">
         <v>35</v>
@@ -2962,7 +2958,7 @@
     </row>
     <row r="13" spans="1:15" ht="18">
       <c r="A13" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="7">
         <v>4</v>
@@ -3128,7 +3124,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -3260,59 +3256,59 @@
         <v>0</v>
       </c>
       <c r="B6" s="1">
-        <f>B9+B7</f>
+        <f t="shared" ref="B6:O6" si="0">B9+B7</f>
         <v>113</v>
       </c>
       <c r="C6" s="1">
-        <f>C9+C7</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="D6" s="1">
-        <f>D9+D7</f>
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="E6" s="1">
-        <f>E9+E7</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F6" s="1">
-        <f>F9+F7</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G6" s="1">
-        <f>G9+G7</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="H6" s="1">
-        <f>H9+H7</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="I6" s="1">
-        <f>I9+I7</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="J6" s="1">
-        <f>J9+J7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <f>K9+K7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <f>L9+L7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <f>M9+M7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <f>N9+N7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <f>O9+O7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3325,61 +3321,61 @@
         <v>111</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" ref="C7:O7" si="0">C8</f>
+        <f t="shared" ref="C7:O7" si="1">C8</f>
         <v>4</v>
       </c>
       <c r="D7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>346</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="18">
       <c r="A8" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="7">
         <v>111</v>
@@ -3426,68 +3422,68 @@
     </row>
     <row r="9" spans="1:15" ht="17.399999999999999">
       <c r="A9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="5">
         <f>SUM(B10:B12)</f>
         <v>2</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" ref="C9:O9" si="1">SUM(C10:C12)</f>
+        <f t="shared" ref="C9:O9" si="2">SUM(C10:C12)</f>
         <v>0</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="18">
       <c r="A10" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="7">
         <v>2</v>
@@ -3653,7 +3649,7 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -3904,7 +3900,7 @@
     </row>
     <row r="8" spans="1:15" ht="18">
       <c r="A8" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="12">
         <v>104</v>
@@ -3951,7 +3947,7 @@
     </row>
     <row r="9" spans="1:15" ht="34.799999999999997">
       <c r="A9" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="5">
         <f>SUM(B10:B19)</f>
@@ -4012,7 +4008,7 @@
     </row>
     <row r="10" spans="1:15" ht="18">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="7">
         <v>74</v>
@@ -4059,7 +4055,7 @@
     </row>
     <row r="11" spans="1:15" ht="18">
       <c r="A11" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="7">
         <v>40</v>
@@ -4106,7 +4102,7 @@
     </row>
     <row r="12" spans="1:15" ht="18">
       <c r="A12" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7">
         <v>47</v>
@@ -4153,7 +4149,7 @@
     </row>
     <row r="13" spans="1:15" ht="18">
       <c r="A13" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="7">
         <v>66</v>
@@ -4200,7 +4196,7 @@
     </row>
     <row r="14" spans="1:15" ht="18">
       <c r="A14" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="10">
         <v>19</v>
@@ -4247,7 +4243,7 @@
     </row>
     <row r="15" spans="1:15" ht="18">
       <c r="A15" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="10">
         <v>3</v>
@@ -4294,7 +4290,7 @@
     </row>
     <row r="16" spans="1:15" ht="18">
       <c r="A16" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="10">
         <v>28</v>
@@ -4341,7 +4337,7 @@
     </row>
     <row r="17" spans="1:15" ht="18">
       <c r="A17" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="7">
         <v>3</v>
